--- a/tables/edgeXcfi_natural.xlsx
+++ b/tables/edgeXcfi_natural.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emmya\Documents\GitHub\OSM_red_squirrel_distribution1\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C47A961B-CEC7-4056-B371-683179759EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF99FCE-102E-4061-B21E-058C3240FB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33705" yWindow="1170" windowWidth="18900" windowHeight="10890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57705" yWindow="2985" windowWidth="18900" windowHeight="10890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="17">
   <si>
     <t>model</t>
   </si>
@@ -40,34 +40,7 @@
     <t>lc_mixedwood</t>
   </si>
   <si>
-    <t>pipe_trans</t>
-  </si>
-  <si>
-    <t>seismic</t>
-  </si>
-  <si>
-    <t>wells_inactive</t>
-  </si>
-  <si>
-    <t>harvest_0_15</t>
-  </si>
-  <si>
-    <t>osm_industrial</t>
-  </si>
-  <si>
-    <t>wells_active</t>
-  </si>
-  <si>
-    <t>landscape_shei</t>
-  </si>
-  <si>
     <t>nonanthro_ed</t>
-  </si>
-  <si>
-    <t>nonanthro_cohesion</t>
-  </si>
-  <si>
-    <t>landscape_mesh</t>
   </si>
   <si>
     <t>cfi_site</t>
@@ -150,7 +123,27 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -161,6 +154,30 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B5B1F974-2963-496E-BA04-D27A41AEEBE5}" name="Table1" displayName="Table1" ref="A1:O19" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:O19" xr:uid="{B5B1F974-2963-496E-BA04-D27A41AEEBE5}"/>
+  <tableColumns count="15">
+    <tableColumn id="1" xr3:uid="{300F23D4-3FF9-4CC8-A7EF-CE0E7D3D5A4E}" name="model"/>
+    <tableColumn id="2" xr3:uid="{7963F9F1-F160-495E-BD34-D98379693FF0}" name="intercept"/>
+    <tableColumn id="3" xr3:uid="{67F1ABB9-744E-4826-885A-33B38170AD41}" name="fire_0_15"/>
+    <tableColumn id="4" xr3:uid="{9BB08301-2C99-48C0-8B44-25FF8C312A1B}" name="lc_broadleaf"/>
+    <tableColumn id="5" xr3:uid="{8911854E-D506-4E54-A1C2-478822BEB987}" name="lc_coniferous"/>
+    <tableColumn id="6" xr3:uid="{5FB60765-F507-48E3-A78A-0B0577838AEE}" name="lc_mixedwood"/>
+    <tableColumn id="7" xr3:uid="{8F1279BE-0EE3-4919-9924-A5828C294953}" name="nonanthro_ed"/>
+    <tableColumn id="8" xr3:uid="{C632F1AC-ABA7-462F-B5A8-6BB6512EBCE4}" name="cfi_site"/>
+    <tableColumn id="9" xr3:uid="{24751B5C-5EAF-43F1-B8A1-5D9C3568C1B6}" name="cfi_site:nonanthro_ed"/>
+    <tableColumn id="10" xr3:uid="{B1E16FB3-4796-4F2A-9FD5-68013374A4B4}" name="df"/>
+    <tableColumn id="11" xr3:uid="{C53546F6-50FC-479D-90B4-655488DE27CA}" name="logLik"/>
+    <tableColumn id="12" xr3:uid="{778A5A8A-071D-481E-B811-1C13ACDACE4D}" name="AICc"/>
+    <tableColumn id="13" xr3:uid="{4CCF9D51-E6F1-444F-8DE7-F4D4B99B6763}" name="delta"/>
+    <tableColumn id="14" xr3:uid="{56B49A47-D4FC-47F6-B133-36DF53EDD953}" name="weight"/>
+    <tableColumn id="15" xr3:uid="{2D8D3288-00F1-4D01-BA72-D34AAAABAB1C}" name="buffer_dist"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -450,13 +467,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.21875" customWidth="1"/>
+    <col min="2" max="3" width="10.88671875" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" customWidth="1"/>
+    <col min="7" max="7" width="18.21875" customWidth="1"/>
+    <col min="8" max="8" width="9.21875" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="15" max="15" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -502,37 +527,10 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>24</v>
       </c>
       <c r="B2">
         <v>-1.567054356409902</v>
@@ -549,72 +547,72 @@
       <c r="F2">
         <v>0.16019909543369421</v>
       </c>
+      <c r="G2">
+        <v>-2.442138517707312E-2</v>
+      </c>
+      <c r="H2">
+        <v>0.26285209422107808</v>
+      </c>
+      <c r="I2">
+        <v>-0.28243274098358001</v>
+      </c>
+      <c r="J2">
+        <v>10</v>
+      </c>
+      <c r="K2">
+        <v>-906.25946029022975</v>
+      </c>
+      <c r="L2">
+        <v>1833.0439802463311</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
       <c r="N2">
-        <v>-2.442138517707312E-2</v>
-      </c>
-      <c r="Q2">
-        <v>0.26285209422107808</v>
-      </c>
-      <c r="R2">
-        <v>-0.28243274098358001</v>
-      </c>
-      <c r="S2">
-        <v>10</v>
-      </c>
-      <c r="T2">
-        <v>-906.25946029022975</v>
-      </c>
-      <c r="U2">
-        <v>1833.0439802463311</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
         <v>0.50029765190115638</v>
       </c>
-      <c r="X2">
+      <c r="O2">
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <v>-1.5742290103925789</v>
       </c>
+      <c r="G3">
+        <v>-0.10043188907387229</v>
+      </c>
+      <c r="H3">
+        <v>0.27844097982140659</v>
+      </c>
+      <c r="I3">
+        <v>-0.26042625433599109</v>
+      </c>
+      <c r="J3">
+        <v>6</v>
+      </c>
+      <c r="K3">
+        <v>-918.56964993567135</v>
+      </c>
+      <c r="L3">
+        <v>1849.3378814316261</v>
+      </c>
+      <c r="M3">
+        <v>16.293901185295681</v>
+      </c>
       <c r="N3">
-        <v>-0.10043188907387229</v>
-      </c>
-      <c r="Q3">
-        <v>0.27844097982140659</v>
-      </c>
-      <c r="R3">
-        <v>-0.26042625433599109</v>
-      </c>
-      <c r="S3">
-        <v>6</v>
-      </c>
-      <c r="T3">
-        <v>-918.56964993567135</v>
-      </c>
-      <c r="U3">
-        <v>1849.3378814316261</v>
-      </c>
-      <c r="V3">
-        <v>16.293901185295681</v>
-      </c>
-      <c r="W3">
         <v>1.4489479269318579E-4</v>
       </c>
-      <c r="X3">
+      <c r="O3">
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B4">
         <v>-1.5341624440190129</v>
@@ -631,72 +629,72 @@
       <c r="F4">
         <v>0.16150258616455271</v>
       </c>
+      <c r="G4">
+        <v>-1.780789592637546E-2</v>
+      </c>
+      <c r="H4">
+        <v>0.31279070838811679</v>
+      </c>
+      <c r="I4">
+        <v>-0.33095293425779693</v>
+      </c>
+      <c r="J4">
+        <v>10</v>
+      </c>
+      <c r="K4">
+        <v>-903.88852219021555</v>
+      </c>
+      <c r="L4">
+        <v>1828.302104046302</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
       <c r="N4">
-        <v>-1.780789592637546E-2</v>
-      </c>
-      <c r="Q4">
-        <v>0.31279070838811679</v>
-      </c>
-      <c r="R4">
-        <v>-0.33095293425779693</v>
-      </c>
-      <c r="S4">
-        <v>10</v>
-      </c>
-      <c r="T4">
-        <v>-903.88852219021555</v>
-      </c>
-      <c r="U4">
-        <v>1828.302104046302</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
         <v>0.92782104659927511</v>
       </c>
-      <c r="X4">
+      <c r="O4">
         <v>1500</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B5">
         <v>-1.5445893000756019</v>
       </c>
+      <c r="G5">
+        <v>-9.4373676942036258E-2</v>
+      </c>
+      <c r="H5">
+        <v>0.3139463221224964</v>
+      </c>
+      <c r="I5">
+        <v>-0.30260828672476758</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>-916.51341809539099</v>
+      </c>
+      <c r="L5">
+        <v>1845.2254177510661</v>
+      </c>
+      <c r="M5">
+        <v>16.923313704763359</v>
+      </c>
       <c r="N5">
-        <v>-9.4373676942036258E-2</v>
-      </c>
-      <c r="Q5">
-        <v>0.3139463221224964</v>
-      </c>
-      <c r="R5">
-        <v>-0.30260828672476758</v>
-      </c>
-      <c r="S5">
-        <v>6</v>
-      </c>
-      <c r="T5">
-        <v>-916.51341809539099</v>
-      </c>
-      <c r="U5">
-        <v>1845.2254177510661</v>
-      </c>
-      <c r="V5">
-        <v>16.923313704763359</v>
-      </c>
-      <c r="W5">
         <v>1.961613045324684E-4</v>
       </c>
-      <c r="X5">
+      <c r="O5">
         <v>1500</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>-1.5487171371619179</v>
@@ -713,72 +711,72 @@
       <c r="F6">
         <v>0.16436419692709089</v>
       </c>
+      <c r="G6">
+        <v>-5.990046606564263E-2</v>
+      </c>
+      <c r="H6">
+        <v>0.34958859713531759</v>
+      </c>
+      <c r="I6">
+        <v>-0.29269890493494533</v>
+      </c>
+      <c r="J6">
+        <v>10</v>
+      </c>
+      <c r="K6">
+        <v>-903.76518201886006</v>
+      </c>
+      <c r="L6">
+        <v>1828.055423703591</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
       <c r="N6">
-        <v>-5.990046606564263E-2</v>
-      </c>
-      <c r="Q6">
-        <v>0.34958859713531759</v>
-      </c>
-      <c r="R6">
-        <v>-0.29269890493494533</v>
-      </c>
-      <c r="S6">
-        <v>10</v>
-      </c>
-      <c r="T6">
-        <v>-903.76518201886006</v>
-      </c>
-      <c r="U6">
-        <v>1828.055423703591</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
         <v>0.86458604080651447</v>
       </c>
-      <c r="X6">
+      <c r="O6">
         <v>2000</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>-1.5591693352414171</v>
       </c>
+      <c r="G7">
+        <v>-0.13860928851731349</v>
+      </c>
+      <c r="H7">
+        <v>0.34216171424404118</v>
+      </c>
+      <c r="I7">
+        <v>-0.26548113176850519</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>-916.42210861517447</v>
+      </c>
+      <c r="L7">
+        <v>1845.042798790633</v>
+      </c>
+      <c r="M7">
+        <v>16.987375087041301</v>
+      </c>
       <c r="N7">
-        <v>-0.13860928851731349</v>
-      </c>
-      <c r="Q7">
-        <v>0.34216171424404118</v>
-      </c>
-      <c r="R7">
-        <v>-0.26548113176850519</v>
-      </c>
-      <c r="S7">
-        <v>6</v>
-      </c>
-      <c r="T7">
-        <v>-916.42210861517447</v>
-      </c>
-      <c r="U7">
-        <v>1845.042798790633</v>
-      </c>
-      <c r="V7">
-        <v>16.987375087041301</v>
-      </c>
-      <c r="W7">
         <v>1.7702988538471481E-4</v>
       </c>
-      <c r="X7">
+      <c r="O7">
         <v>2000</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B8">
         <v>-1.5708402998977331</v>
@@ -795,72 +793,72 @@
       <c r="F8">
         <v>0.1672482465817203</v>
       </c>
+      <c r="G8">
+        <v>-8.8036524560268684E-2</v>
+      </c>
+      <c r="H8">
+        <v>0.33823670989403049</v>
+      </c>
+      <c r="I8">
+        <v>-0.25288603364962298</v>
+      </c>
+      <c r="J8">
+        <v>10</v>
+      </c>
+      <c r="K8">
+        <v>-904.51857334135775</v>
+      </c>
+      <c r="L8">
+        <v>1829.5622063485871</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
       <c r="N8">
-        <v>-8.8036524560268684E-2</v>
-      </c>
-      <c r="Q8">
-        <v>0.33823670989403049</v>
-      </c>
-      <c r="R8">
-        <v>-0.25288603364962298</v>
-      </c>
-      <c r="S8">
-        <v>10</v>
-      </c>
-      <c r="T8">
-        <v>-904.51857334135775</v>
-      </c>
-      <c r="U8">
-        <v>1829.5622063485871</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
         <v>0.74555299328160851</v>
       </c>
-      <c r="X8">
+      <c r="O8">
         <v>2500</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>-1.580360849362977</v>
       </c>
+      <c r="G9">
+        <v>-0.17061083989807979</v>
+      </c>
+      <c r="H9">
+        <v>0.33118913568234459</v>
+      </c>
+      <c r="I9">
+        <v>-0.2279779464426272</v>
+      </c>
+      <c r="J9">
+        <v>6</v>
+      </c>
+      <c r="K9">
+        <v>-917.0193651577988</v>
+      </c>
+      <c r="L9">
+        <v>1846.237311875881</v>
+      </c>
+      <c r="M9">
+        <v>16.675105527294591</v>
+      </c>
       <c r="N9">
-        <v>-0.17061083989807979</v>
-      </c>
-      <c r="Q9">
-        <v>0.33118913568234459</v>
-      </c>
-      <c r="R9">
-        <v>-0.2279779464426272</v>
-      </c>
-      <c r="S9">
-        <v>6</v>
-      </c>
-      <c r="T9">
-        <v>-917.0193651577988</v>
-      </c>
-      <c r="U9">
-        <v>1846.237311875881</v>
-      </c>
-      <c r="V9">
-        <v>16.675105527294591</v>
-      </c>
-      <c r="W9">
         <v>1.784536192331156E-4</v>
       </c>
-      <c r="X9">
+      <c r="O9">
         <v>2500</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>-1.5764741052358999</v>
@@ -877,72 +875,72 @@
       <c r="F10">
         <v>0.16914927821944789</v>
       </c>
+      <c r="G10">
+        <v>-0.1049512444848595</v>
+      </c>
+      <c r="H10">
+        <v>0.36140806690596872</v>
+      </c>
+      <c r="I10">
+        <v>-0.2352072667109148</v>
+      </c>
+      <c r="J10">
+        <v>10</v>
+      </c>
+      <c r="K10">
+        <v>-904.27780852866886</v>
+      </c>
+      <c r="L10">
+        <v>1829.0806767232091</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
       <c r="N10">
-        <v>-0.1049512444848595</v>
-      </c>
-      <c r="Q10">
-        <v>0.36140806690596872</v>
-      </c>
-      <c r="R10">
-        <v>-0.2352072667109148</v>
-      </c>
-      <c r="S10">
-        <v>10</v>
-      </c>
-      <c r="T10">
-        <v>-904.27780852866886</v>
-      </c>
-      <c r="U10">
-        <v>1829.0806767232091</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
         <v>0.73186976221716527</v>
       </c>
-      <c r="X10">
+      <c r="O10">
         <v>3000</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>-1.586746369046893</v>
       </c>
+      <c r="G11">
+        <v>-0.19360580260053109</v>
+      </c>
+      <c r="H11">
+        <v>0.35141376535061281</v>
+      </c>
+      <c r="I11">
+        <v>-0.2103207706975532</v>
+      </c>
+      <c r="J11">
+        <v>6</v>
+      </c>
+      <c r="K11">
+        <v>-916.83561508789967</v>
+      </c>
+      <c r="L11">
+        <v>1845.869811736083</v>
+      </c>
+      <c r="M11">
+        <v>16.789135012874109</v>
+      </c>
       <c r="N11">
-        <v>-0.19360580260053109</v>
-      </c>
-      <c r="Q11">
-        <v>0.35141376535061281</v>
-      </c>
-      <c r="R11">
-        <v>-0.2103207706975532</v>
-      </c>
-      <c r="S11">
-        <v>6</v>
-      </c>
-      <c r="T11">
-        <v>-916.83561508789967</v>
-      </c>
-      <c r="U11">
-        <v>1845.869811736083</v>
-      </c>
-      <c r="V11">
-        <v>16.789135012874109</v>
-      </c>
-      <c r="W11">
         <v>1.654700729233999E-4</v>
       </c>
-      <c r="X11">
+      <c r="O11">
         <v>3000</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B12">
         <v>-1.5835550595121179</v>
@@ -959,72 +957,72 @@
       <c r="F12">
         <v>0.17038263368965889</v>
       </c>
+      <c r="G12">
+        <v>-0.12664692329833391</v>
+      </c>
+      <c r="H12">
+        <v>0.37605743374146122</v>
+      </c>
+      <c r="I12">
+        <v>-0.21377694196648159</v>
+      </c>
+      <c r="J12">
+        <v>10</v>
+      </c>
+      <c r="K12">
+        <v>-904.56563219632653</v>
+      </c>
+      <c r="L12">
+        <v>1829.656324058524</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
       <c r="N12">
-        <v>-0.12664692329833391</v>
-      </c>
-      <c r="Q12">
-        <v>0.37605743374146122</v>
-      </c>
-      <c r="R12">
-        <v>-0.21377694196648159</v>
-      </c>
-      <c r="S12">
-        <v>10</v>
-      </c>
-      <c r="T12">
-        <v>-904.56563219632653</v>
-      </c>
-      <c r="U12">
-        <v>1829.656324058524</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
         <v>0.62375766021014756</v>
       </c>
-      <c r="X12">
+      <c r="O12">
         <v>3500</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>-1.598192695553178</v>
       </c>
+      <c r="G13">
+        <v>-0.23469767556460611</v>
+      </c>
+      <c r="H13">
+        <v>0.36691664361760651</v>
+      </c>
+      <c r="I13">
+        <v>-0.18318049471821229</v>
+      </c>
+      <c r="J13">
+        <v>6</v>
+      </c>
+      <c r="K13">
+        <v>-917.06922023141783</v>
+      </c>
+      <c r="L13">
+        <v>1846.3370220231191</v>
+      </c>
+      <c r="M13">
+        <v>16.68069796459508</v>
+      </c>
       <c r="N13">
-        <v>-0.23469767556460611</v>
-      </c>
-      <c r="Q13">
-        <v>0.36691664361760651</v>
-      </c>
-      <c r="R13">
-        <v>-0.18318049471821229</v>
-      </c>
-      <c r="S13">
-        <v>6</v>
-      </c>
-      <c r="T13">
-        <v>-917.06922023141783</v>
-      </c>
-      <c r="U13">
-        <v>1846.3370220231191</v>
-      </c>
-      <c r="V13">
-        <v>16.68069796459508</v>
-      </c>
-      <c r="W13">
         <v>1.4888411096689131E-4</v>
       </c>
-      <c r="X13">
+      <c r="O13">
         <v>3500</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B14">
         <v>-1.5868657143877429</v>
@@ -1041,72 +1039,72 @@
       <c r="F14">
         <v>0.17047079065131249</v>
       </c>
+      <c r="G14">
+        <v>-0.1507517109222988</v>
+      </c>
+      <c r="H14">
+        <v>0.38198133800314538</v>
+      </c>
+      <c r="I14">
+        <v>-0.20387521053389679</v>
+      </c>
+      <c r="J14">
+        <v>10</v>
+      </c>
+      <c r="K14">
+        <v>-904.65456205060104</v>
+      </c>
+      <c r="L14">
+        <v>1829.834183767073</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
       <c r="N14">
-        <v>-0.1507517109222988</v>
-      </c>
-      <c r="Q14">
-        <v>0.38198133800314538</v>
-      </c>
-      <c r="R14">
-        <v>-0.20387521053389679</v>
-      </c>
-      <c r="S14">
-        <v>10</v>
-      </c>
-      <c r="T14">
-        <v>-904.65456205060104</v>
-      </c>
-      <c r="U14">
-        <v>1829.834183767073</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
         <v>0.50635100882777606</v>
       </c>
-      <c r="X14">
+      <c r="O14">
         <v>4000</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B15">
         <v>-1.6062464452890031</v>
       </c>
+      <c r="G15">
+        <v>-0.27349749578301757</v>
+      </c>
+      <c r="H15">
+        <v>0.36921437010673269</v>
+      </c>
+      <c r="I15">
+        <v>-0.1664237061338385</v>
+      </c>
+      <c r="J15">
+        <v>6</v>
+      </c>
+      <c r="K15">
+        <v>-917.17344720262645</v>
+      </c>
+      <c r="L15">
+        <v>1846.545475965537</v>
+      </c>
+      <c r="M15">
+        <v>16.711292198463301</v>
+      </c>
       <c r="N15">
-        <v>-0.27349749578301757</v>
-      </c>
-      <c r="Q15">
-        <v>0.36921437010673269</v>
-      </c>
-      <c r="R15">
-        <v>-0.1664237061338385</v>
-      </c>
-      <c r="S15">
-        <v>6</v>
-      </c>
-      <c r="T15">
-        <v>-917.17344720262645</v>
-      </c>
-      <c r="U15">
-        <v>1846.545475965537</v>
-      </c>
-      <c r="V15">
-        <v>16.711292198463301</v>
-      </c>
-      <c r="W15">
         <v>1.1902568401470309E-4</v>
       </c>
-      <c r="X15">
+      <c r="O15">
         <v>4000</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B16">
         <v>-1.601143910735096</v>
@@ -1123,72 +1121,72 @@
       <c r="F16">
         <v>0.17164211480752081</v>
       </c>
+      <c r="G16">
+        <v>-0.18722902244422401</v>
+      </c>
+      <c r="H16">
+        <v>0.38149256219928401</v>
+      </c>
+      <c r="I16">
+        <v>-0.17997588574242521</v>
+      </c>
+      <c r="J16">
+        <v>10</v>
+      </c>
+      <c r="K16">
+        <v>-905.11407138656136</v>
+      </c>
+      <c r="L16">
+        <v>1830.7532024389941</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
       <c r="N16">
-        <v>-0.18722902244422401</v>
-      </c>
-      <c r="Q16">
-        <v>0.38149256219928401</v>
-      </c>
-      <c r="R16">
-        <v>-0.17997588574242521</v>
-      </c>
-      <c r="S16">
-        <v>10</v>
-      </c>
-      <c r="T16">
-        <v>-905.11407138656136</v>
-      </c>
-      <c r="U16">
-        <v>1830.7532024389941</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
         <v>0.36466636472707581</v>
       </c>
-      <c r="X16">
+      <c r="O16">
         <v>4500</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B17">
         <v>-1.6220427267259121</v>
       </c>
+      <c r="G17">
+        <v>-0.31207372760937602</v>
+      </c>
+      <c r="H17">
+        <v>0.35774258964418659</v>
+      </c>
+      <c r="I17">
+        <v>-0.13974218642300781</v>
+      </c>
+      <c r="J17">
+        <v>6</v>
+      </c>
+      <c r="K17">
+        <v>-917.69589637413151</v>
+      </c>
+      <c r="L17">
+        <v>1847.5903743085471</v>
+      </c>
+      <c r="M17">
+        <v>16.83717186955278</v>
+      </c>
       <c r="N17">
-        <v>-0.31207372760937602</v>
-      </c>
-      <c r="Q17">
-        <v>0.35774258964418659</v>
-      </c>
-      <c r="R17">
-        <v>-0.13974218642300781</v>
-      </c>
-      <c r="S17">
-        <v>6</v>
-      </c>
-      <c r="T17">
-        <v>-917.69589637413151</v>
-      </c>
-      <c r="U17">
-        <v>1847.5903743085471</v>
-      </c>
-      <c r="V17">
-        <v>16.83717186955278</v>
-      </c>
-      <c r="W17">
         <v>8.0491550045117186E-5</v>
       </c>
-      <c r="X17">
+      <c r="O17">
         <v>4500</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B18">
         <v>-1.624133942636955</v>
@@ -1205,70 +1203,74 @@
       <c r="F18">
         <v>0.17351680641497991</v>
       </c>
+      <c r="G18">
+        <v>-0.24264872476319141</v>
+      </c>
+      <c r="H18">
+        <v>0.37908417657227927</v>
+      </c>
+      <c r="I18">
+        <v>-0.14268792336865049</v>
+      </c>
+      <c r="J18">
+        <v>10</v>
+      </c>
+      <c r="K18">
+        <v>-905.64489725954331</v>
+      </c>
+      <c r="L18">
+        <v>1831.814854184958</v>
+      </c>
+      <c r="M18">
+        <v>0.24815883554242649</v>
+      </c>
       <c r="N18">
-        <v>-0.24264872476319141</v>
-      </c>
-      <c r="Q18">
-        <v>0.37908417657227927</v>
-      </c>
-      <c r="R18">
-        <v>-0.14268792336865049</v>
-      </c>
-      <c r="S18">
-        <v>10</v>
-      </c>
-      <c r="T18">
-        <v>-905.64489725954331</v>
-      </c>
-      <c r="U18">
-        <v>1831.814854184958</v>
-      </c>
-      <c r="V18">
-        <v>0.24815883554242649</v>
-      </c>
-      <c r="W18">
         <v>0.24132184422628999</v>
       </c>
-      <c r="X18">
+      <c r="O18">
         <v>5000</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B19">
         <v>-1.6475005054687659</v>
       </c>
+      <c r="G19">
+        <v>-0.37171455512288393</v>
+      </c>
+      <c r="H19">
+        <v>0.34422871934650839</v>
+      </c>
+      <c r="I19">
+        <v>-9.7822702492103647E-2</v>
+      </c>
+      <c r="J19">
+        <v>6</v>
+      </c>
+      <c r="K19">
+        <v>-918.25504371051375</v>
+      </c>
+      <c r="L19">
+        <v>1848.7086689813109</v>
+      </c>
+      <c r="M19">
+        <v>17.14197363189578</v>
+      </c>
       <c r="N19">
-        <v>-0.37171455512288393</v>
-      </c>
-      <c r="Q19">
-        <v>0.34422871934650839</v>
-      </c>
-      <c r="R19">
-        <v>-9.7822702492103647E-2</v>
-      </c>
-      <c r="S19">
-        <v>6</v>
-      </c>
-      <c r="T19">
-        <v>-918.25504371051375</v>
-      </c>
-      <c r="U19">
-        <v>1848.7086689813109</v>
-      </c>
-      <c r="V19">
-        <v>17.14197363189578</v>
-      </c>
-      <c r="W19">
         <v>5.1778726345168668E-5</v>
       </c>
-      <c r="X19">
+      <c r="O19">
         <v>5000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>